--- a/engine/publish_queue/SWDY/SWDY_Valuation_Model_05082026_public.xlsx
+++ b/engine/publish_queue/SWDY/SWDY_Valuation_Model_05082026_public.xlsx
@@ -808,7 +808,7 @@
     <row r="42">
       <c r="A42" s="3" t="inlineStr">
         <is>
-          <t>26.9% -&gt; 15.9% on the same easing calendar as the interest forecast; the terminal value is</t>
+          <t>28.8% -&gt; 17.2% on the same easing calendar as the interest forecast; the terminal value is</t>
         </is>
       </c>
     </row>
@@ -2556,111 +2556,111 @@
     <row r="6">
       <c r="A6" s="6" t="inlineStr">
         <is>
-          <t>13.9%</t>
+          <t>15.2%</t>
         </is>
       </c>
       <c r="B6" s="7" t="n">
-        <v>64.92380553045649</v>
+        <v>54.89390300698878</v>
       </c>
       <c r="C6" s="7" t="n">
-        <v>67.81454330477681</v>
+        <v>56.76608049282878</v>
       </c>
       <c r="D6" s="7" t="n">
-        <v>71.2657550153391</v>
+        <v>58.9328825766538</v>
       </c>
       <c r="E6" s="7" t="n">
-        <v>75.48936116950645</v>
+        <v>61.49018601091854</v>
       </c>
       <c r="F6" s="7" t="n">
-        <v>80.81952864869957</v>
+        <v>64.58052940682644</v>
       </c>
     </row>
     <row r="7">
       <c r="A7" s="6" t="inlineStr">
         <is>
-          <t>14.9%</t>
+          <t>16.2%</t>
         </is>
       </c>
       <c r="B7" s="7" t="n">
-        <v>58.18280778459938</v>
+        <v>49.59394363429544</v>
       </c>
       <c r="C7" s="7" t="n">
-        <v>60.28097444263505</v>
+        <v>50.95326657112403</v>
       </c>
       <c r="D7" s="7" t="n">
-        <v>62.7254596302354</v>
+        <v>52.49104063008191</v>
       </c>
       <c r="E7" s="7" t="n">
-        <v>65.6325529341344</v>
+        <v>54.25965459765457</v>
       </c>
       <c r="F7" s="7" t="n">
-        <v>69.17717086762013</v>
+        <v>56.33422840926579</v>
       </c>
     </row>
     <row r="8">
       <c r="A8" s="6" t="inlineStr">
         <is>
-          <t>15.9%</t>
+          <t>17.2%</t>
         </is>
       </c>
       <c r="B8" s="7" t="n">
-        <v>52.49799810153853</v>
+        <v>45.05103667309857</v>
       </c>
       <c r="C8" s="7" t="n">
-        <v>54.02258879276857</v>
+        <v>46.03042217002906</v>
       </c>
       <c r="D8" s="7" t="n">
-        <v>55.75852138598012</v>
+        <v>47.11281563256473</v>
       </c>
       <c r="E8" s="7" t="n">
-        <v>57.76961833972243</v>
+        <v>48.32576211063959</v>
       </c>
       <c r="F8" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.7075887045515</v>
       </c>
     </row>
     <row r="9">
       <c r="A9" s="6" t="inlineStr">
         <is>
-          <t>16.9%</t>
+          <t>18.2%</t>
         </is>
       </c>
       <c r="B9" s="7" t="n">
-        <v>47.64148809789273</v>
+        <v>41.11553668357441</v>
       </c>
       <c r="C9" s="7" t="n">
-        <v>48.74316174823518</v>
+        <v>41.8093978775642</v>
       </c>
       <c r="D9" s="7" t="n">
-        <v>49.96902514555856</v>
+        <v>42.55648627630665</v>
       </c>
       <c r="E9" s="7" t="n">
-        <v>51.3531520126963</v>
+        <v>43.36987034045674</v>
       </c>
       <c r="F9" s="7" t="n">
-        <v>52.94333582385958</v>
+        <v>44.26727799429032</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="6" t="inlineStr">
         <is>
-          <t>17.9%</t>
+          <t>19.2%</t>
         </is>
       </c>
       <c r="B10" s="7" t="n">
-        <v>43.44644775731468</v>
+        <v>37.67472174247933</v>
       </c>
       <c r="C10" s="7" t="n">
-        <v>44.23152271678764</v>
+        <v>38.15151148948571</v>
       </c>
       <c r="D10" s="7" t="n">
-        <v>45.08351233414617</v>
+        <v>38.648345329237</v>
       </c>
       <c r="E10" s="7" t="n">
-        <v>46.01923749436355</v>
+        <v>39.16977223986016</v>
       </c>
       <c r="F10" s="7" t="n">
-        <v>47.06167257131559</v>
+        <v>39.72183036633324</v>
       </c>
     </row>
     <row r="12">
@@ -2674,138 +2674,138 @@
       <c r="A13" s="5" t="inlineStr"/>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>23.9%</t>
+          <t>25.8%</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>25.4%</t>
+          <t>27.3%</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>26.9%</t>
+          <t>28.8%</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
         <is>
-          <t>28.4%</t>
+          <t>30.3%</t>
         </is>
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>29.9%</t>
+          <t>31.8%</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="6" t="inlineStr">
         <is>
-          <t>terminal 13.9%</t>
+          <t>terminal 15.2%</t>
         </is>
       </c>
       <c r="B14" s="7" t="n">
-        <v>85.84545509208399</v>
+        <v>68.64247049591957</v>
       </c>
       <c r="C14" s="7" t="n">
-        <v>83.28726331486288</v>
+        <v>66.57546829677946</v>
       </c>
       <c r="D14" s="7" t="n">
-        <v>80.81952864869957</v>
+        <v>64.58052940682644</v>
       </c>
       <c r="E14" s="7" t="n">
-        <v>78.43825692508688</v>
+        <v>62.65451643723234</v>
       </c>
       <c r="F14" s="7" t="n">
-        <v>76.13966662860086</v>
+        <v>60.79445670792633</v>
       </c>
     </row>
     <row r="15">
       <c r="A15" s="6" t="inlineStr">
         <is>
-          <t>terminal 14.9%</t>
+          <t>terminal 16.2%</t>
         </is>
       </c>
       <c r="B15" s="7" t="n">
-        <v>73.5404678355972</v>
+        <v>59.93237666911776</v>
       </c>
       <c r="C15" s="7" t="n">
-        <v>71.31963462621358</v>
+        <v>58.10144964510826</v>
       </c>
       <c r="D15" s="7" t="n">
-        <v>69.17717086762013</v>
+        <v>56.33422840926579</v>
       </c>
       <c r="E15" s="7" t="n">
-        <v>67.10962173729665</v>
+        <v>54.62794387184755</v>
       </c>
       <c r="F15" s="7" t="n">
-        <v>65.11371611583073</v>
+        <v>52.9799721331991</v>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="6" t="inlineStr">
         <is>
-          <t>terminal 15.9%</t>
+          <t>terminal 17.2%</t>
         </is>
       </c>
       <c r="B16" s="7" t="n">
-        <v>63.99790976465807</v>
+        <v>52.93321441251824</v>
       </c>
       <c r="C16" s="7" t="n">
-        <v>62.03859171613212</v>
+        <v>51.2919036374145</v>
       </c>
       <c r="D16" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.7075887045515</v>
       </c>
       <c r="E16" s="7" t="n">
-        <v>58.32392716970243</v>
+        <v>48.17779610598239</v>
       </c>
       <c r="F16" s="7" t="n">
-        <v>56.56266789121253</v>
+        <v>46.70018186414503</v>
       </c>
     </row>
     <row r="17">
       <c r="A17" s="6" t="inlineStr">
         <is>
-          <t>terminal 16.9%</t>
+          <t>terminal 18.2%</t>
         </is>
       </c>
       <c r="B17" s="7" t="n">
-        <v>56.3832632823887</v>
+        <v>47.18722756407969</v>
       </c>
       <c r="C17" s="7" t="n">
-        <v>54.63253200536953</v>
+        <v>45.70150653374164</v>
       </c>
       <c r="D17" s="7" t="n">
-        <v>52.94333582385958</v>
+        <v>44.26727799429032</v>
       </c>
       <c r="E17" s="7" t="n">
-        <v>51.31297067571722</v>
+        <v>42.88231076920474</v>
       </c>
       <c r="F17" s="7" t="n">
-        <v>49.73887592188827</v>
+        <v>41.54449037834811</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" s="6" t="inlineStr">
         <is>
-          <t>terminal 17.9%</t>
+          <t>terminal 19.2%</t>
         </is>
       </c>
       <c r="B18" s="7" t="n">
-        <v>50.16731028865568</v>
+        <v>42.38652255248041</v>
       </c>
       <c r="C18" s="7" t="n">
-        <v>48.58676906627794</v>
+        <v>41.03072689368742</v>
       </c>
       <c r="D18" s="7" t="n">
-        <v>47.06167257131559</v>
+        <v>39.72183036633324</v>
       </c>
       <c r="E18" s="7" t="n">
-        <v>45.58958818858307</v>
+        <v>38.45780396819539</v>
       </c>
       <c r="F18" s="7" t="n">
-        <v>44.16821216991782</v>
+        <v>37.23672469018629</v>
       </c>
     </row>
     <row r="20">
@@ -2836,23 +2836,23 @@
     <row r="22">
       <c r="A22" s="6" t="inlineStr">
         <is>
-          <t>Beta  (0.60 / 0.80 / 1.01 / 1.15 / 1.30)</t>
+          <t>Beta  (0.60 / 0.80 / 1.23 / 1.15 / 1.30)</t>
         </is>
       </c>
       <c r="B22" s="7" t="n">
-        <v>93.45277355246162</v>
+        <v>94.46647146810956</v>
       </c>
       <c r="C22" s="7" t="n">
-        <v>74.44674244752112</v>
+        <v>75.25828072607085</v>
       </c>
       <c r="D22" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.70341773987482</v>
       </c>
       <c r="E22" s="7" t="n">
-        <v>52.63301422037497</v>
+        <v>53.21252849781632</v>
       </c>
       <c r="F22" s="7" t="n">
-        <v>45.99373037705359</v>
+        <v>46.50262521769896</v>
       </c>
       <c r="H22" s="16">
         <f>MAX(B22:F22)-MIN(B22:F22)</f>
@@ -2866,19 +2866,19 @@
         </is>
       </c>
       <c r="B23" s="7" t="n">
-        <v>50.79365382947766</v>
+        <v>42.07500523515485</v>
       </c>
       <c r="C23" s="7" t="n">
-        <v>52.69688996099238</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>56.50336222402186</v>
+        <v>46.38227967442072</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>61.26145255280872</v>
+        <v>49.97167504047564</v>
       </c>
       <c r="F23" s="7" t="n">
-        <v>66.01954288159557</v>
+        <v>53.56107040653055</v>
       </c>
       <c r="H23" s="16">
         <f>MAX(B23:F23)-MIN(B23:F23)</f>
@@ -2892,19 +2892,19 @@
         </is>
       </c>
       <c r="B24" s="7" t="n">
-        <v>29.48174706762489</v>
+        <v>23.17689166022818</v>
       </c>
       <c r="C24" s="7" t="n">
-        <v>41.08931851430866</v>
+        <v>33.3438275209025</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>52.69688996099238</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>64.30446140767616</v>
+        <v>53.67769924225113</v>
       </c>
       <c r="F24" s="7" t="n">
-        <v>75.91203285435989</v>
+        <v>63.84463510292543</v>
       </c>
       <c r="H24" s="16">
         <f>MAX(B24:F24)-MIN(B24:F24)</f>
@@ -2918,19 +2918,19 @@
         </is>
       </c>
       <c r="B25" s="7" t="n">
-        <v>49.8420357637203</v>
+        <v>41.3571261619439</v>
       </c>
       <c r="C25" s="7" t="n">
-        <v>51.26946286235632</v>
+        <v>42.43394477176034</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>52.69688996099238</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>54.12431705962842</v>
+        <v>44.58758199139326</v>
       </c>
       <c r="F25" s="7" t="n">
-        <v>55.55174415826449</v>
+        <v>45.66440060120974</v>
       </c>
       <c r="H25" s="16">
         <f>MAX(B25:F25)-MIN(B25:F25)</f>
@@ -2944,19 +2944,19 @@
         </is>
       </c>
       <c r="B26" s="7" t="n">
-        <v>59.90563209825564</v>
+        <v>50.27171997464177</v>
       </c>
       <c r="C26" s="7" t="n">
-        <v>56.17697237208499</v>
+        <v>46.77467346098749</v>
       </c>
       <c r="D26" s="7" t="n">
-        <v>52.69688996099238</v>
+        <v>43.51076338157681</v>
       </c>
       <c r="E26" s="7" t="n">
-        <v>48.71965291974369</v>
+        <v>39.7805804336789</v>
       </c>
       <c r="F26" s="7" t="n">
-        <v>44.99099319357304</v>
+        <v>36.28353392002459</v>
       </c>
       <c r="H26" s="16">
         <f>MAX(B26:F26)-MIN(B26:F26)</f>
@@ -2970,19 +2970,19 @@
         </is>
       </c>
       <c r="B27" s="7" t="n">
-        <v>49.62272921986233</v>
+        <v>40.98127111072365</v>
       </c>
       <c r="C27" s="7" t="n">
-        <v>56.53511112692783</v>
+        <v>46.71205527626227</v>
       </c>
       <c r="D27" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.7075887045515</v>
       </c>
       <c r="E27" s="7" t="n">
-        <v>67.16954483010554</v>
+        <v>55.52864630016783</v>
       </c>
       <c r="F27" s="7" t="n">
-        <v>70.35987494105883</v>
+        <v>58.17362360733951</v>
       </c>
       <c r="H27" s="16">
         <f>MAX(B27:F27)-MIN(B27:F27)</f>
@@ -2996,19 +2996,19 @@
         </is>
       </c>
       <c r="B28" s="7" t="n">
-        <v>52.49799810153853</v>
+        <v>45.05103667309857</v>
       </c>
       <c r="C28" s="7" t="n">
-        <v>54.02258879276857</v>
+        <v>46.03042217002906</v>
       </c>
       <c r="D28" s="7" t="n">
-        <v>55.75852138598012</v>
+        <v>47.11281563256473</v>
       </c>
       <c r="E28" s="7" t="n">
-        <v>57.76961833972243</v>
+        <v>48.32576211063959</v>
       </c>
       <c r="F28" s="7" t="n">
-        <v>60.14827652865958</v>
+        <v>49.7075887045515</v>
       </c>
       <c r="H28" s="16">
         <f>MAX(B28:F28)-MIN(B28:F28)</f>
@@ -4015,14 +4015,14 @@
         </is>
       </c>
       <c r="B5" s="7" t="n">
-        <v>19.63802419176771</v>
+        <v>16.18162005664932</v>
       </c>
       <c r="C5" s="8">
         <f>DCF!C62</f>
         <v/>
       </c>
       <c r="D5" s="7" t="n">
-        <v>101.3067584343183</v>
+        <v>83.79876343050132</v>
       </c>
       <c r="E5" s="6" t="inlineStr">
         <is>
@@ -4428,7 +4428,7 @@
         </is>
       </c>
       <c r="C6" s="7" t="n">
-        <v>19.63802419176771</v>
+        <v>16.18162005664932</v>
       </c>
     </row>
     <row r="7">
@@ -4443,7 +4443,7 @@
         </is>
       </c>
       <c r="C7" s="7" t="n">
-        <v>101.3067584343183</v>
+        <v>83.79876343050132</v>
       </c>
     </row>
     <row r="8">
@@ -4531,7 +4531,7 @@
       </c>
       <c r="C16" s="22" t="inlineStr">
         <is>
-          <t>26.9% → 15.9%</t>
+          <t>28.8% → 17.2%</t>
         </is>
       </c>
     </row>
@@ -4553,7 +4553,7 @@
         </is>
       </c>
       <c r="C18" s="7" t="n">
-        <v>70.84778269949645</v>
+        <v>57.86095793273499</v>
       </c>
     </row>
     <row r="19">
@@ -4613,13 +4613,13 @@
         </is>
       </c>
       <c r="C23" s="7" t="n">
-        <v>151.4223547712553</v>
+        <v>153.052652198775</v>
       </c>
       <c r="D23" s="7" t="n">
-        <v>111.0875245682934</v>
+        <v>112.2887963569921</v>
       </c>
       <c r="E23" s="7" t="n">
-        <v>191.7571849742172</v>
+        <v>193.8165080405579</v>
       </c>
     </row>
     <row r="24">
@@ -4634,13 +4634,13 @@
         </is>
       </c>
       <c r="C24" s="7" t="n">
-        <v>74.30796795435184</v>
+        <v>65.48394099946414</v>
       </c>
       <c r="D24" s="7" t="n">
-        <v>36.90047424542561</v>
+        <v>34.12367903228015</v>
       </c>
       <c r="E24" s="7" t="n">
-        <v>67.07141566856639</v>
+        <v>59.75270243066323</v>
       </c>
     </row>
     <row r="25">
@@ -4655,13 +4655,13 @@
         </is>
       </c>
       <c r="C25" s="7" t="n">
-        <v>55.21683864604976</v>
+        <v>45.28950840983638</v>
       </c>
       <c r="D25" s="7" t="n">
-        <v>47.64716300797847</v>
+        <v>42.22747080432825</v>
       </c>
       <c r="E25" s="7" t="n">
-        <v>70.84778269949645</v>
+        <v>57.86095793273499</v>
       </c>
     </row>
     <row r="26">
@@ -5152,7 +5152,7 @@
         </is>
       </c>
       <c r="C33" s="26" t="n">
-        <v>1.009</v>
+        <v>1.224906574047969</v>
       </c>
     </row>
     <row r="34">
